--- a/BOM Provisional _Elisa Washer.xlsx
+++ b/BOM Provisional _Elisa Washer.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shing\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B63FA-8B58-4225-84F3-8ABB5D494643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF50BE7D-C5C3-4D6A-AA2F-2A01C1367439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1893,21 +1882,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I127"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="84.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="29.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="91"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="84.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="29.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="91"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B1" s="60"/>
       <c r="C1" s="23"/>
       <c r="D1" s="24" t="s">
@@ -1916,7 +1905,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
     </row>
-    <row r="2" spans="1:9" s="33" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="33" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1932,7 @@
       </c>
       <c r="I2" s="31"/>
     </row>
-    <row r="3" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="8"/>
       <c r="C3" s="13"/>
@@ -1954,7 +1943,7 @@
       <c r="H3" s="83"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="16"/>
       <c r="C4" s="44" t="s">
@@ -1969,7 +1958,7 @@
       <c r="H4" s="84"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="62" t="s">
         <v>158</v>
@@ -1990,7 +1979,7 @@
       <c r="H5" s="83"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="62" t="s">
         <v>159</v>
@@ -2011,7 +2000,7 @@
       <c r="H6" s="83"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="62" t="s">
         <v>160</v>
@@ -2032,7 +2021,7 @@
       <c r="H7" s="83"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="62" t="s">
         <v>199</v>
@@ -2053,7 +2042,7 @@
       <c r="H8" s="83"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="64" t="s">
         <v>157</v>
@@ -2076,7 +2065,7 @@
       </c>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="4" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="16"/>
       <c r="C10" s="36"/>
@@ -2095,7 +2084,7 @@
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="16"/>
       <c r="C11" s="14"/>
@@ -2106,7 +2095,7 @@
       <c r="H11" s="83"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="16"/>
       <c r="C12" s="44" t="s">
@@ -2120,7 +2109,7 @@
       <c r="G12" s="71"/>
       <c r="H12" s="84"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="62" t="s">
         <v>161</v>
@@ -2140,7 +2129,7 @@
       <c r="G13" s="29"/>
       <c r="H13" s="83"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="62" t="s">
         <v>162</v>
@@ -2160,7 +2149,7 @@
       <c r="G14" s="29"/>
       <c r="H14" s="83"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="62" t="s">
         <v>163</v>
@@ -2180,7 +2169,7 @@
       <c r="G15" s="29"/>
       <c r="H15" s="83"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="62" t="s">
         <v>164</v>
@@ -2200,7 +2189,7 @@
       <c r="G16" s="29"/>
       <c r="H16" s="83"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="62" t="s">
         <v>165</v>
@@ -2220,7 +2209,7 @@
       <c r="G17" s="29"/>
       <c r="H17" s="83"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="62" t="s">
         <v>166</v>
@@ -2240,7 +2229,7 @@
       <c r="G18" s="29"/>
       <c r="H18" s="83"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="16" t="s">
         <v>145</v>
@@ -2262,7 +2251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="30" t="s">
         <v>146</v>
@@ -2284,7 +2273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="78" t="s">
         <v>211</v>
@@ -2304,7 +2293,7 @@
       <c r="G21" s="72"/>
       <c r="H21" s="88"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="78" t="s">
         <v>212</v>
@@ -2324,7 +2313,7 @@
       <c r="G22" s="72"/>
       <c r="H22" s="88"/>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="79" t="s">
         <v>213</v>
@@ -2345,7 +2334,7 @@
       <c r="H23" s="88"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -2362,7 +2351,7 @@
       <c r="H24" s="88"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2379,7 +2368,7 @@
       <c r="H25" s="88"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2396,7 +2385,7 @@
       <c r="H26" s="88"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="30"/>
       <c r="C27" s="16"/>
@@ -2413,7 +2402,7 @@
       <c r="H27" s="88"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="30"/>
       <c r="C28" s="16"/>
@@ -2430,7 +2419,7 @@
       <c r="H28" s="88"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" s="30"/>
       <c r="C29" s="36"/>
@@ -2447,7 +2436,7 @@
       <c r="H29" s="88"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" s="30"/>
       <c r="C30" s="16"/>
@@ -2458,7 +2447,7 @@
       <c r="H30" s="83"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="16"/>
       <c r="C31" s="44" t="s">
@@ -2473,7 +2462,7 @@
       <c r="H31" s="84"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="63" t="s">
         <v>167</v>
@@ -2493,7 +2482,7 @@
       <c r="G32" s="29"/>
       <c r="H32" s="83"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="63" t="s">
         <v>168</v>
@@ -2513,7 +2502,7 @@
       <c r="G33" s="29"/>
       <c r="H33" s="83"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="63" t="s">
         <v>169</v>
@@ -2536,7 +2525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="63" t="s">
         <v>170</v>
@@ -2556,7 +2545,7 @@
       <c r="G35" s="29"/>
       <c r="H35" s="83"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="63" t="s">
         <v>171</v>
@@ -2576,7 +2565,7 @@
       <c r="G36" s="29"/>
       <c r="H36" s="83"/>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="16" t="s">
         <v>141</v>
@@ -2597,9 +2586,11 @@
       <c r="H37" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I37" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="30" t="s">
         <v>140</v>
@@ -2620,9 +2611,11 @@
       <c r="H38" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I38" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" s="30" t="s">
         <v>153</v>
@@ -2645,7 +2638,7 @@
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:9" s="4" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" s="4" customFormat="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="30" t="s">
         <v>208</v>
@@ -2666,7 +2659,7 @@
       <c r="H40" s="89"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="41" spans="1:9" s="4" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="80" t="s">
         <v>216</v>
@@ -2689,7 +2682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="30"/>
       <c r="C42" s="50"/>
@@ -2706,7 +2699,7 @@
       <c r="H42" s="89"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
       <c r="B43" s="16" t="s">
         <v>200</v>
@@ -2729,7 +2722,7 @@
       </c>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" s="30"/>
       <c r="C44" s="16"/>
@@ -2740,7 +2733,7 @@
       <c r="H44" s="83"/>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" s="30"/>
       <c r="C45" s="44" t="s">
@@ -2755,7 +2748,7 @@
       <c r="H45" s="84"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
       <c r="B46" s="63" t="s">
         <v>172</v>
@@ -2776,7 +2769,7 @@
       <c r="H46" s="83"/>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="5"/>
       <c r="B47" s="63" t="s">
         <v>173</v>
@@ -2797,7 +2790,7 @@
       <c r="H47" s="83"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A48" s="5"/>
       <c r="B48" s="63" t="s">
         <v>174</v>
@@ -2818,7 +2811,7 @@
       <c r="H48" s="83"/>
       <c r="I48" s="7"/>
     </row>
-    <row r="49" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="5"/>
       <c r="B49" s="63" t="s">
         <v>175</v>
@@ -2839,7 +2832,7 @@
       <c r="H49" s="83"/>
       <c r="I49" s="7"/>
     </row>
-    <row r="50" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="5"/>
       <c r="B50" s="16" t="s">
         <v>147</v>
@@ -2860,9 +2853,11 @@
       <c r="H50" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I50" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
       <c r="B51" s="16" t="s">
         <v>205</v>
@@ -2885,7 +2880,7 @@
       </c>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5"/>
       <c r="B52" s="16" t="s">
         <v>204</v>
@@ -2906,7 +2901,7 @@
       <c r="H52" s="83"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="53" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -2917,7 +2912,7 @@
       <c r="H53" s="83"/>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
       <c r="B54" s="16"/>
       <c r="C54" s="44" t="s">
@@ -2932,7 +2927,7 @@
       <c r="H54" s="84"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="63" t="s">
         <v>176</v>
@@ -2951,9 +2946,11 @@
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="83"/>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I55" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="63" t="s">
         <v>177</v>
@@ -2972,9 +2969,11 @@
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="83"/>
-      <c r="I56" s="7"/>
-    </row>
-    <row r="57" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I56" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="63" t="s">
         <v>178</v>
@@ -2993,9 +2992,11 @@
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="83"/>
-      <c r="I57" s="7"/>
-    </row>
-    <row r="58" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I57" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="63" t="s">
         <v>179</v>
@@ -3016,7 +3017,7 @@
       <c r="H58" s="83"/>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="63" t="s">
         <v>180</v>
@@ -3035,9 +3036,11 @@
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="83"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="60" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I59" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="63" t="s">
         <v>181</v>
@@ -3058,7 +3061,7 @@
       <c r="H60" s="83"/>
       <c r="I60" s="7"/>
     </row>
-    <row r="61" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="63" t="s">
         <v>182</v>
@@ -3077,9 +3080,11 @@
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="83"/>
-      <c r="I61" s="7"/>
-    </row>
-    <row r="62" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I61" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="63" t="s">
         <v>183</v>
@@ -3100,7 +3105,7 @@
       <c r="H62" s="83"/>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="16" t="s">
         <v>148</v>
@@ -3123,7 +3128,7 @@
       </c>
       <c r="I63" s="7"/>
     </row>
-    <row r="64" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="16" t="s">
         <v>149</v>
@@ -3146,7 +3151,7 @@
       </c>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="16" t="s">
         <v>150</v>
@@ -3169,7 +3174,7 @@
       </c>
       <c r="I65" s="7"/>
     </row>
-    <row r="66" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="61" t="s">
         <v>184</v>
@@ -3192,7 +3197,7 @@
       </c>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A67" s="5"/>
       <c r="B67" s="16" t="s">
         <v>200</v>
@@ -3215,7 +3220,7 @@
       </c>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A68" s="5"/>
       <c r="B68" s="16"/>
       <c r="C68" s="36"/>
@@ -3232,7 +3237,7 @@
       <c r="H68" s="88"/>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A69" s="5"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -3243,7 +3248,7 @@
       <c r="H69" s="83"/>
       <c r="I69" s="7"/>
     </row>
-    <row r="70" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" s="16"/>
       <c r="C70" s="44" t="s">
@@ -3258,7 +3263,7 @@
       <c r="H70" s="84"/>
       <c r="I70" s="7"/>
     </row>
-    <row r="71" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A71" s="5"/>
       <c r="B71" s="16" t="s">
         <v>151</v>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A72" s="5"/>
       <c r="B72" s="16" t="s">
         <v>152</v>
@@ -3304,7 +3309,7 @@
       </c>
       <c r="I72" s="7"/>
     </row>
-    <row r="73" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A73" s="5"/>
       <c r="B73" s="16" t="s">
         <v>206</v>
@@ -3327,7 +3332,7 @@
       </c>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A74" s="5"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -3338,7 +3343,7 @@
       <c r="H74" s="83"/>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="16"/>
       <c r="C75" s="44" t="s">
@@ -3353,7 +3358,7 @@
       <c r="H75" s="84"/>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A76" s="5"/>
       <c r="B76" s="63" t="s">
         <v>185</v>
@@ -3374,7 +3379,7 @@
       <c r="H76" s="83"/>
       <c r="I76" s="7"/>
     </row>
-    <row r="77" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A77" s="5"/>
       <c r="B77" s="63" t="s">
         <v>186</v>
@@ -3395,7 +3400,7 @@
       <c r="H77" s="83"/>
       <c r="I77" s="7"/>
     </row>
-    <row r="78" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A78" s="5"/>
       <c r="B78" s="63" t="s">
         <v>187</v>
@@ -3416,7 +3421,7 @@
       <c r="H78" s="83"/>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A79" s="5"/>
       <c r="B79" s="63" t="s">
         <v>188</v>
@@ -3437,7 +3442,7 @@
       <c r="H79" s="83"/>
       <c r="I79" s="7"/>
     </row>
-    <row r="80" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A80" s="5"/>
       <c r="B80" s="63" t="s">
         <v>189</v>
@@ -3458,7 +3463,7 @@
       <c r="H80" s="83"/>
       <c r="I80" s="7"/>
     </row>
-    <row r="81" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A81" s="5"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -3469,7 +3474,7 @@
       <c r="H81" s="83"/>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="16"/>
       <c r="C82" s="44" t="s">
@@ -3484,7 +3489,7 @@
       <c r="H82" s="84"/>
       <c r="I82" s="7"/>
     </row>
-    <row r="83" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A83" s="5"/>
       <c r="B83" s="63" t="s">
         <v>190</v>
@@ -3505,7 +3510,7 @@
       <c r="H83" s="83"/>
       <c r="I83" s="7"/>
     </row>
-    <row r="84" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="5"/>
       <c r="B84" s="63" t="s">
         <v>186</v>
@@ -3526,7 +3531,7 @@
       <c r="H84" s="83"/>
       <c r="I84" s="7"/>
     </row>
-    <row r="85" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A85" s="5"/>
       <c r="B85" s="63" t="s">
         <v>187</v>
@@ -3547,7 +3552,7 @@
       <c r="H85" s="83"/>
       <c r="I85" s="7"/>
     </row>
-    <row r="86" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A86" s="5"/>
       <c r="B86" s="63" t="s">
         <v>188</v>
@@ -3568,7 +3573,7 @@
       <c r="H86" s="83"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A87" s="5"/>
       <c r="B87" s="63" t="s">
         <v>189</v>
@@ -3589,7 +3594,7 @@
       <c r="H87" s="83"/>
       <c r="I87" s="7"/>
     </row>
-    <row r="88" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="5"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -3600,7 +3605,7 @@
       <c r="H88" s="83"/>
       <c r="I88" s="7"/>
     </row>
-    <row r="89" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5"/>
       <c r="B89" s="16"/>
       <c r="C89" s="44" t="s">
@@ -3615,7 +3620,7 @@
       <c r="H89" s="90"/>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A90" s="5"/>
       <c r="B90" s="61" t="s">
         <v>191</v>
@@ -3636,7 +3641,7 @@
       <c r="H90" s="83"/>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="61" t="s">
         <v>192</v>
@@ -3656,7 +3661,7 @@
       <c r="G91" s="29"/>
       <c r="H91" s="83"/>
     </row>
-    <row r="92" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A92" s="5"/>
       <c r="B92" s="61" t="s">
         <v>193</v>
@@ -3677,7 +3682,7 @@
       <c r="H92" s="83"/>
       <c r="I92" s="7"/>
     </row>
-    <row r="93" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5"/>
       <c r="B93" s="16"/>
       <c r="C93" s="19"/>
@@ -3688,7 +3693,7 @@
       <c r="H93" s="83"/>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5"/>
       <c r="B94" s="16"/>
       <c r="C94" s="19"/>
@@ -3699,7 +3704,7 @@
       <c r="H94" s="83"/>
       <c r="I94" s="7"/>
     </row>
-    <row r="95" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5"/>
       <c r="B95" s="16"/>
       <c r="C95" s="19"/>
@@ -3710,7 +3715,7 @@
       <c r="H95" s="83"/>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5"/>
       <c r="B96" s="16"/>
       <c r="C96" s="19"/>
@@ -3721,7 +3726,7 @@
       <c r="H96" s="83"/>
       <c r="I96" s="7"/>
     </row>
-    <row r="97" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5"/>
       <c r="B97" s="16"/>
       <c r="C97" s="19"/>
@@ -3732,7 +3737,7 @@
       <c r="H97" s="83"/>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5"/>
       <c r="B98" s="16"/>
       <c r="C98" s="19"/>
@@ -3743,7 +3748,7 @@
       <c r="H98" s="83"/>
       <c r="I98" s="7"/>
     </row>
-    <row r="99" spans="1:9" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A99" s="5"/>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
@@ -3754,7 +3759,7 @@
       <c r="H99" s="83"/>
       <c r="I99" s="7"/>
     </row>
-    <row r="100" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5"/>
       <c r="B100" s="16"/>
       <c r="C100" s="19"/>
@@ -3765,7 +3770,7 @@
       <c r="H100" s="83"/>
       <c r="I100" s="7"/>
     </row>
-    <row r="101" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5"/>
       <c r="B101" s="16"/>
       <c r="C101" s="19"/>
@@ -3776,7 +3781,7 @@
       <c r="H101" s="83"/>
       <c r="I101" s="7"/>
     </row>
-    <row r="102" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5"/>
       <c r="B102" s="16"/>
       <c r="C102" s="19"/>
@@ -3787,7 +3792,7 @@
       <c r="H102" s="83"/>
       <c r="I102" s="7"/>
     </row>
-    <row r="103" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5"/>
       <c r="B103" s="16"/>
       <c r="C103" s="19"/>
@@ -3798,7 +3803,7 @@
       <c r="H103" s="83"/>
       <c r="I103" s="7"/>
     </row>
-    <row r="104" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5"/>
       <c r="B104" s="16"/>
       <c r="C104" s="19"/>
@@ -3809,7 +3814,7 @@
       <c r="H104" s="83"/>
       <c r="I104" s="7"/>
     </row>
-    <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="16"/>
       <c r="C105" s="19"/>
@@ -3819,7 +3824,7 @@
       <c r="G105" s="29"/>
       <c r="H105" s="83"/>
     </row>
-    <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="16"/>
       <c r="C106" s="19"/>
@@ -3829,7 +3834,7 @@
       <c r="G106" s="29"/>
       <c r="H106" s="83"/>
     </row>
-    <row r="107" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5"/>
       <c r="B107" s="16"/>
       <c r="C107" s="19"/>
@@ -3840,7 +3845,7 @@
       <c r="H107" s="83"/>
       <c r="I107" s="7"/>
     </row>
-    <row r="108" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5"/>
       <c r="B108" s="16"/>
       <c r="C108" s="19"/>
@@ -3851,7 +3856,7 @@
       <c r="H108" s="83"/>
       <c r="I108" s="7"/>
     </row>
-    <row r="109" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5"/>
       <c r="B109" s="16"/>
       <c r="C109" s="19"/>
@@ -3862,7 +3867,7 @@
       <c r="H109" s="83"/>
       <c r="I109" s="7"/>
     </row>
-    <row r="110" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5"/>
       <c r="B110" s="16"/>
       <c r="C110" s="19"/>
@@ -3873,7 +3878,7 @@
       <c r="H110" s="83"/>
       <c r="I110" s="7"/>
     </row>
-    <row r="111" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5"/>
       <c r="B111" s="16"/>
       <c r="C111" s="19"/>
@@ -3884,7 +3889,7 @@
       <c r="H111" s="83"/>
       <c r="I111" s="7"/>
     </row>
-    <row r="112" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5"/>
       <c r="B112" s="16"/>
       <c r="C112" s="19"/>
@@ -3895,7 +3900,7 @@
       <c r="H112" s="83"/>
       <c r="I112" s="7"/>
     </row>
-    <row r="113" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
       <c r="B113" s="16"/>
       <c r="C113" s="19"/>
@@ -3906,7 +3911,7 @@
       <c r="H113" s="83"/>
       <c r="I113" s="7"/>
     </row>
-    <row r="114" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5"/>
       <c r="B114" s="16"/>
       <c r="C114" s="19"/>
@@ -3917,7 +3922,7 @@
       <c r="H114" s="83"/>
       <c r="I114" s="7"/>
     </row>
-    <row r="115" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5"/>
       <c r="B115" s="16"/>
       <c r="C115" s="19"/>
@@ -3928,7 +3933,7 @@
       <c r="H115" s="83"/>
       <c r="I115" s="7"/>
     </row>
-    <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="16"/>
       <c r="C116" s="19"/>
@@ -3938,7 +3943,7 @@
       <c r="G116" s="29"/>
       <c r="H116" s="83"/>
     </row>
-    <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="16"/>
       <c r="C117" s="19"/>
@@ -3948,7 +3953,7 @@
       <c r="G117" s="29"/>
       <c r="H117" s="83"/>
     </row>
-    <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="16"/>
       <c r="C118" s="19"/>
@@ -3958,7 +3963,7 @@
       <c r="G118" s="29"/>
       <c r="H118" s="83"/>
     </row>
-    <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="16"/>
       <c r="C119" s="19"/>
@@ -3968,7 +3973,7 @@
       <c r="G119" s="29"/>
       <c r="H119" s="83"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
@@ -3978,7 +3983,7 @@
       <c r="G120" s="29"/>
       <c r="H120" s="83"/>
     </row>
-    <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="16"/>
       <c r="C121" s="19"/>
@@ -3988,7 +3993,7 @@
       <c r="G121" s="29"/>
       <c r="H121" s="83"/>
     </row>
-    <row r="122" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
       <c r="B122" s="16"/>
       <c r="C122" s="19"/>
@@ -3999,7 +4004,7 @@
       <c r="H122" s="83"/>
       <c r="I122" s="7"/>
     </row>
-    <row r="123" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
       <c r="B123" s="16"/>
       <c r="C123" s="19"/>
@@ -4010,7 +4015,7 @@
       <c r="H123" s="83"/>
       <c r="I123" s="7"/>
     </row>
-    <row r="124" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5"/>
       <c r="B124" s="16"/>
       <c r="C124" s="19"/>
@@ -4021,7 +4026,7 @@
       <c r="H124" s="83"/>
       <c r="I124" s="7"/>
     </row>
-    <row r="125" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5"/>
       <c r="B125" s="16"/>
       <c r="C125" s="19"/>
@@ -4032,7 +4037,7 @@
       <c r="H125" s="83"/>
       <c r="I125" s="7"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
@@ -4042,7 +4047,7 @@
       <c r="G126" s="29"/>
       <c r="H126" s="83"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
@@ -4136,19 +4141,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
@@ -4159,7 +4164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -4170,7 +4175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>2</v>
       </c>
@@ -4181,7 +4186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>3</v>
       </c>
@@ -4192,7 +4197,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>4</v>
       </c>
@@ -4203,7 +4208,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>5</v>
       </c>
@@ -4214,7 +4219,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>6</v>
       </c>
@@ -4225,7 +4230,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>7</v>
       </c>
@@ -4236,7 +4241,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>8</v>
       </c>
@@ -4247,7 +4252,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>9</v>
       </c>

--- a/BOM Provisional _Elisa Washer.xlsx
+++ b/BOM Provisional _Elisa Washer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF50BE7D-C5C3-4D6A-AA2F-2A01C1367439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D01C772-0298-4A33-8254-B32A1D94E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1126,9 +1126,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1145,6 +1142,9 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1892,7 +1892,7 @@
     <col min="6" max="6" width="9.85546875" style="15" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="29.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="91"/>
+    <col min="9" max="9" width="8.85546875" style="90"/>
     <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
@@ -1927,7 +1927,7 @@
       <c r="G2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="81" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="31"/>
@@ -1940,7 +1940,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="13"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="83"/>
+      <c r="H3" s="82"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1955,7 +1955,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
       <c r="G4" s="49"/>
-      <c r="H4" s="84"/>
+      <c r="H4" s="83"/>
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="83"/>
+      <c r="H5" s="82"/>
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -1997,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="83"/>
+      <c r="H6" s="82"/>
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2018,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="83"/>
+      <c r="H7" s="82"/>
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2039,7 +2039,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="83"/>
+      <c r="H8" s="82"/>
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2060,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="68"/>
-      <c r="H9" s="85" t="s">
+      <c r="H9" s="84" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="7"/>
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="37"/>
-      <c r="H10" s="86" t="s">
+      <c r="H10" s="85" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="7"/>
@@ -2092,7 +2092,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="14"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="83"/>
+      <c r="H11" s="82"/>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2107,7 +2107,7 @@
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="71"/>
-      <c r="H12" s="84"/>
+      <c r="H12" s="83"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -2127,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="29"/>
-      <c r="H13" s="83"/>
+      <c r="H13" s="82"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="29"/>
-      <c r="H14" s="83"/>
+      <c r="H14" s="82"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="29"/>
-      <c r="H15" s="83"/>
+      <c r="H15" s="82"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="29"/>
-      <c r="H16" s="83"/>
+      <c r="H16" s="82"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="29"/>
-      <c r="H17" s="83"/>
+      <c r="H17" s="82"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="29"/>
-      <c r="H18" s="83"/>
+      <c r="H18" s="82"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -2247,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="72"/>
-      <c r="H19" s="87" t="s">
+      <c r="H19" s="86" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="G20" s="72"/>
-      <c r="H20" s="88" t="s">
+      <c r="H20" s="87" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="72"/>
-      <c r="H21" s="88"/>
+      <c r="H21" s="87"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="72"/>
-      <c r="H22" s="88"/>
+      <c r="H22" s="87"/>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
@@ -2331,7 +2331,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="39"/>
-      <c r="H23" s="88"/>
+      <c r="H23" s="87"/>
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="39"/>
-      <c r="H24" s="88"/>
+      <c r="H24" s="87"/>
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2365,7 +2365,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="39"/>
-      <c r="H25" s="88"/>
+      <c r="H25" s="87"/>
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2382,7 +2382,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="39"/>
-      <c r="H26" s="88"/>
+      <c r="H26" s="87"/>
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2399,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="39"/>
-      <c r="H27" s="88"/>
+      <c r="H27" s="87"/>
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2416,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="39"/>
-      <c r="H28" s="88"/>
+      <c r="H28" s="87"/>
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2433,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="39"/>
-      <c r="H29" s="88"/>
+      <c r="H29" s="87"/>
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2444,7 +2444,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="16"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="83"/>
+      <c r="H30" s="82"/>
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2459,7 +2459,7 @@
       <c r="E31" s="26"/>
       <c r="F31" s="26"/>
       <c r="G31" s="49"/>
-      <c r="H31" s="84"/>
+      <c r="H31" s="83"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="29"/>
-      <c r="H32" s="83"/>
+      <c r="H32" s="82"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -2500,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="29"/>
-      <c r="H33" s="83"/>
+      <c r="H33" s="82"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
@@ -2520,8 +2520,8 @@
         <v>1</v>
       </c>
       <c r="G34" s="29"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="91">
+      <c r="H34" s="82"/>
+      <c r="I34" s="90">
         <v>5</v>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="29"/>
-      <c r="H35" s="83"/>
+      <c r="H35" s="82"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -2563,7 +2563,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="29"/>
-      <c r="H36" s="83"/>
+      <c r="H36" s="82"/>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="39"/>
-      <c r="H37" s="88" t="s">
+      <c r="H37" s="87" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="7">
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="39"/>
-      <c r="H38" s="88" t="s">
+      <c r="H38" s="87" t="s">
         <v>63</v>
       </c>
       <c r="I38" s="7">
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="39"/>
-      <c r="H39" s="88" t="s">
+      <c r="H39" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I39" s="7"/>
@@ -2656,15 +2656,15 @@
         <v>1</v>
       </c>
       <c r="G40" s="51"/>
-      <c r="H40" s="89"/>
+      <c r="H40" s="88"/>
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="91" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="81" t="s">
+      <c r="C41" s="80" t="s">
         <v>215</v>
       </c>
       <c r="D41" s="75" t="s">
@@ -2677,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="51"/>
-      <c r="H41" s="89"/>
+      <c r="H41" s="88"/>
       <c r="I41" s="7">
         <v>5</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="51"/>
-      <c r="H42" s="89"/>
+      <c r="H42" s="88"/>
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2717,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="39"/>
-      <c r="H43" s="88" t="s">
+      <c r="H43" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I43" s="7"/>
@@ -2730,7 +2730,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="16"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="83"/>
+      <c r="H44" s="82"/>
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2745,7 +2745,7 @@
       <c r="E45" s="26"/>
       <c r="F45" s="26"/>
       <c r="G45" s="49"/>
-      <c r="H45" s="84"/>
+      <c r="H45" s="83"/>
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5"/>
-      <c r="H46" s="83"/>
+      <c r="H46" s="82"/>
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5"/>
-      <c r="H47" s="83"/>
+      <c r="H47" s="82"/>
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="5"/>
-      <c r="H48" s="83"/>
+      <c r="H48" s="82"/>
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2829,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="5"/>
-      <c r="H49" s="83"/>
+      <c r="H49" s="82"/>
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2850,7 +2850,7 @@
         <v>2</v>
       </c>
       <c r="G50" s="39"/>
-      <c r="H50" s="88" t="s">
+      <c r="H50" s="87" t="s">
         <v>63</v>
       </c>
       <c r="I50" s="7">
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="39"/>
-      <c r="H51" s="88" t="s">
+      <c r="H51" s="87" t="s">
         <v>63</v>
       </c>
       <c r="I51" s="7"/>
@@ -2898,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="5"/>
-      <c r="H52" s="83"/>
+      <c r="H52" s="82"/>
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2909,7 +2909,7 @@
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="83"/>
+      <c r="H53" s="82"/>
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2924,7 +2924,7 @@
       <c r="E54" s="26"/>
       <c r="F54" s="26"/>
       <c r="G54" s="49"/>
-      <c r="H54" s="84"/>
+      <c r="H54" s="83"/>
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -2945,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="83"/>
+      <c r="H55" s="82"/>
       <c r="I55" s="7">
         <v>5</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="5"/>
-      <c r="H56" s="83"/>
+      <c r="H56" s="82"/>
       <c r="I56" s="7">
         <v>5</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5"/>
-      <c r="H57" s="83"/>
+      <c r="H57" s="82"/>
       <c r="I57" s="7">
         <v>5</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="5"/>
-      <c r="H58" s="83"/>
+      <c r="H58" s="82"/>
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5"/>
-      <c r="H59" s="83"/>
+      <c r="H59" s="82"/>
       <c r="I59" s="7">
         <v>5</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="5"/>
-      <c r="H60" s="83"/>
+      <c r="H60" s="82"/>
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3079,7 +3079,7 @@
         <v>2</v>
       </c>
       <c r="G61" s="5"/>
-      <c r="H61" s="83"/>
+      <c r="H61" s="82"/>
       <c r="I61" s="7">
         <v>10</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="5"/>
-      <c r="H62" s="83"/>
+      <c r="H62" s="82"/>
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3123,7 +3123,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="48"/>
-      <c r="H63" s="87" t="s">
+      <c r="H63" s="86" t="s">
         <v>33</v>
       </c>
       <c r="I63" s="7"/>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="48"/>
-      <c r="H64" s="88" t="s">
+      <c r="H64" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I64" s="7"/>
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="39"/>
-      <c r="H65" s="88" t="s">
+      <c r="H65" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I65" s="7"/>
@@ -3192,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="39"/>
-      <c r="H66" s="88" t="s">
+      <c r="H66" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I66" s="7"/>
@@ -3215,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="39"/>
-      <c r="H67" s="88" t="s">
+      <c r="H67" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I67" s="7"/>
@@ -3234,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="39"/>
-      <c r="H68" s="88"/>
+      <c r="H68" s="87"/>
       <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3245,7 +3245,7 @@
       <c r="E69" s="7"/>
       <c r="F69" s="16"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="83"/>
+      <c r="H69" s="82"/>
       <c r="I69" s="7"/>
     </row>
     <row r="70" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3260,7 +3260,7 @@
       <c r="E70" s="26"/>
       <c r="F70" s="44"/>
       <c r="G70" s="49"/>
-      <c r="H70" s="84"/>
+      <c r="H70" s="83"/>
       <c r="I70" s="7"/>
     </row>
     <row r="71" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3281,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="39"/>
-      <c r="H71" s="88" t="s">
+      <c r="H71" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I71" s="7"/>
@@ -3304,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="39"/>
-      <c r="H72" s="88" t="s">
+      <c r="H72" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I72" s="7"/>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
       <c r="G73" s="39"/>
-      <c r="H73" s="88" t="s">
+      <c r="H73" s="87" t="s">
         <v>33</v>
       </c>
       <c r="I73" s="7"/>
@@ -3340,7 +3340,7 @@
       <c r="E74" s="7"/>
       <c r="F74" s="16"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="83"/>
+      <c r="H74" s="82"/>
       <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
       <c r="E75" s="26"/>
       <c r="F75" s="44"/>
       <c r="G75" s="49"/>
-      <c r="H75" s="84"/>
+      <c r="H75" s="83"/>
       <c r="I75" s="7"/>
     </row>
     <row r="76" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3376,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="5"/>
-      <c r="H76" s="83"/>
+      <c r="H76" s="82"/>
       <c r="I76" s="7"/>
     </row>
     <row r="77" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3397,7 +3397,7 @@
         <v>12</v>
       </c>
       <c r="G77" s="5"/>
-      <c r="H77" s="83"/>
+      <c r="H77" s="82"/>
       <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3418,7 +3418,7 @@
         <v>12</v>
       </c>
       <c r="G78" s="5"/>
-      <c r="H78" s="83"/>
+      <c r="H78" s="82"/>
       <c r="I78" s="7"/>
     </row>
     <row r="79" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3439,7 +3439,7 @@
         <v>4</v>
       </c>
       <c r="G79" s="5"/>
-      <c r="H79" s="83"/>
+      <c r="H79" s="82"/>
       <c r="I79" s="7"/>
     </row>
     <row r="80" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3460,7 +3460,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="5"/>
-      <c r="H80" s="83"/>
+      <c r="H80" s="82"/>
       <c r="I80" s="7"/>
     </row>
     <row r="81" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3471,7 +3471,7 @@
       <c r="E81" s="7"/>
       <c r="F81" s="16"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="83"/>
+      <c r="H81" s="82"/>
       <c r="I81" s="7"/>
     </row>
     <row r="82" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3486,7 +3486,7 @@
       <c r="E82" s="26"/>
       <c r="F82" s="44"/>
       <c r="G82" s="49"/>
-      <c r="H82" s="84"/>
+      <c r="H82" s="83"/>
       <c r="I82" s="7"/>
     </row>
     <row r="83" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3507,7 +3507,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="5"/>
-      <c r="H83" s="83"/>
+      <c r="H83" s="82"/>
       <c r="I83" s="7"/>
     </row>
     <row r="84" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3528,7 +3528,7 @@
         <v>12</v>
       </c>
       <c r="G84" s="5"/>
-      <c r="H84" s="83"/>
+      <c r="H84" s="82"/>
       <c r="I84" s="7"/>
     </row>
     <row r="85" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3549,7 +3549,7 @@
         <v>12</v>
       </c>
       <c r="G85" s="5"/>
-      <c r="H85" s="83"/>
+      <c r="H85" s="82"/>
       <c r="I85" s="7"/>
     </row>
     <row r="86" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3570,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="G86" s="5"/>
-      <c r="H86" s="83"/>
+      <c r="H86" s="82"/>
       <c r="I86" s="7"/>
     </row>
     <row r="87" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3591,7 +3591,7 @@
         <v>2</v>
       </c>
       <c r="G87" s="5"/>
-      <c r="H87" s="83"/>
+      <c r="H87" s="82"/>
       <c r="I87" s="7"/>
     </row>
     <row r="88" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3602,7 +3602,7 @@
       <c r="E88" s="7"/>
       <c r="F88" s="16"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="83"/>
+      <c r="H88" s="82"/>
       <c r="I88" s="7"/>
     </row>
     <row r="89" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3617,7 +3617,7 @@
       <c r="E89" s="26"/>
       <c r="F89" s="52"/>
       <c r="G89" s="54"/>
-      <c r="H89" s="90"/>
+      <c r="H89" s="89"/>
       <c r="I89" s="7"/>
     </row>
     <row r="90" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="5"/>
-      <c r="H90" s="83"/>
+      <c r="H90" s="82"/>
       <c r="I90" s="7"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3659,7 +3659,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="29"/>
-      <c r="H91" s="83"/>
+      <c r="H91" s="82"/>
     </row>
     <row r="92" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A92" s="5"/>
@@ -3679,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="5"/>
-      <c r="H92" s="83"/>
+      <c r="H92" s="82"/>
       <c r="I92" s="7"/>
     </row>
     <row r="93" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3690,7 +3690,7 @@
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="5"/>
-      <c r="H93" s="83"/>
+      <c r="H93" s="82"/>
       <c r="I93" s="7"/>
     </row>
     <row r="94" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3701,7 +3701,7 @@
       <c r="E94" s="7"/>
       <c r="F94" s="16"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="83"/>
+      <c r="H94" s="82"/>
       <c r="I94" s="7"/>
     </row>
     <row r="95" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3712,7 +3712,7 @@
       <c r="E95" s="7"/>
       <c r="F95" s="16"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="83"/>
+      <c r="H95" s="82"/>
       <c r="I95" s="7"/>
     </row>
     <row r="96" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3723,7 +3723,7 @@
       <c r="E96" s="7"/>
       <c r="F96" s="16"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="83"/>
+      <c r="H96" s="82"/>
       <c r="I96" s="7"/>
     </row>
     <row r="97" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3734,7 +3734,7 @@
       <c r="E97" s="7"/>
       <c r="F97" s="16"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="83"/>
+      <c r="H97" s="82"/>
       <c r="I97" s="7"/>
     </row>
     <row r="98" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3745,7 +3745,7 @@
       <c r="E98" s="7"/>
       <c r="F98" s="16"/>
       <c r="G98" s="5"/>
-      <c r="H98" s="83"/>
+      <c r="H98" s="82"/>
       <c r="I98" s="7"/>
     </row>
     <row r="99" spans="1:9" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3756,7 +3756,7 @@
       <c r="E99" s="7"/>
       <c r="F99" s="16"/>
       <c r="G99" s="5"/>
-      <c r="H99" s="83"/>
+      <c r="H99" s="82"/>
       <c r="I99" s="7"/>
     </row>
     <row r="100" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3767,7 +3767,7 @@
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
       <c r="G100" s="5"/>
-      <c r="H100" s="83"/>
+      <c r="H100" s="82"/>
       <c r="I100" s="7"/>
     </row>
     <row r="101" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3778,7 +3778,7 @@
       <c r="E101" s="7"/>
       <c r="F101" s="16"/>
       <c r="G101" s="5"/>
-      <c r="H101" s="83"/>
+      <c r="H101" s="82"/>
       <c r="I101" s="7"/>
     </row>
     <row r="102" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3789,7 +3789,7 @@
       <c r="E102" s="7"/>
       <c r="F102" s="16"/>
       <c r="G102" s="5"/>
-      <c r="H102" s="83"/>
+      <c r="H102" s="82"/>
       <c r="I102" s="7"/>
     </row>
     <row r="103" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3800,7 +3800,7 @@
       <c r="E103" s="7"/>
       <c r="F103" s="16"/>
       <c r="G103" s="5"/>
-      <c r="H103" s="83"/>
+      <c r="H103" s="82"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3811,7 +3811,7 @@
       <c r="E104" s="7"/>
       <c r="F104" s="16"/>
       <c r="G104" s="5"/>
-      <c r="H104" s="83"/>
+      <c r="H104" s="82"/>
       <c r="I104" s="7"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -3822,7 +3822,7 @@
       <c r="E105" s="7"/>
       <c r="F105" s="16"/>
       <c r="G105" s="29"/>
-      <c r="H105" s="83"/>
+      <c r="H105" s="82"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
@@ -3832,7 +3832,7 @@
       <c r="E106" s="7"/>
       <c r="F106" s="16"/>
       <c r="G106" s="29"/>
-      <c r="H106" s="83"/>
+      <c r="H106" s="82"/>
     </row>
     <row r="107" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5"/>
@@ -3842,7 +3842,7 @@
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
       <c r="G107" s="5"/>
-      <c r="H107" s="83"/>
+      <c r="H107" s="82"/>
       <c r="I107" s="7"/>
     </row>
     <row r="108" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3853,7 +3853,7 @@
       <c r="E108" s="7"/>
       <c r="F108" s="16"/>
       <c r="G108" s="5"/>
-      <c r="H108" s="83"/>
+      <c r="H108" s="82"/>
       <c r="I108" s="7"/>
     </row>
     <row r="109" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3864,7 +3864,7 @@
       <c r="E109" s="7"/>
       <c r="F109" s="16"/>
       <c r="G109" s="5"/>
-      <c r="H109" s="83"/>
+      <c r="H109" s="82"/>
       <c r="I109" s="7"/>
     </row>
     <row r="110" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3875,7 +3875,7 @@
       <c r="E110" s="7"/>
       <c r="F110" s="16"/>
       <c r="G110" s="5"/>
-      <c r="H110" s="83"/>
+      <c r="H110" s="82"/>
       <c r="I110" s="7"/>
     </row>
     <row r="111" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3886,7 +3886,7 @@
       <c r="E111" s="7"/>
       <c r="F111" s="16"/>
       <c r="G111" s="28"/>
-      <c r="H111" s="83"/>
+      <c r="H111" s="82"/>
       <c r="I111" s="7"/>
     </row>
     <row r="112" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3897,7 +3897,7 @@
       <c r="E112" s="7"/>
       <c r="F112" s="16"/>
       <c r="G112" s="28"/>
-      <c r="H112" s="83"/>
+      <c r="H112" s="82"/>
       <c r="I112" s="7"/>
     </row>
     <row r="113" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3908,7 +3908,7 @@
       <c r="E113" s="7"/>
       <c r="F113" s="16"/>
       <c r="G113" s="28"/>
-      <c r="H113" s="83"/>
+      <c r="H113" s="82"/>
       <c r="I113" s="7"/>
     </row>
     <row r="114" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3919,7 +3919,7 @@
       <c r="E114" s="7"/>
       <c r="F114" s="16"/>
       <c r="G114" s="5"/>
-      <c r="H114" s="83"/>
+      <c r="H114" s="82"/>
       <c r="I114" s="7"/>
     </row>
     <row r="115" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3930,7 +3930,7 @@
       <c r="E115" s="7"/>
       <c r="F115" s="16"/>
       <c r="G115" s="5"/>
-      <c r="H115" s="83"/>
+      <c r="H115" s="82"/>
       <c r="I115" s="7"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -3941,7 +3941,7 @@
       <c r="E116" s="7"/>
       <c r="F116" s="14"/>
       <c r="G116" s="29"/>
-      <c r="H116" s="83"/>
+      <c r="H116" s="82"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
@@ -3951,7 +3951,7 @@
       <c r="E117" s="7"/>
       <c r="F117" s="16"/>
       <c r="G117" s="29"/>
-      <c r="H117" s="83"/>
+      <c r="H117" s="82"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
@@ -3961,7 +3961,7 @@
       <c r="E118" s="7"/>
       <c r="F118" s="16"/>
       <c r="G118" s="29"/>
-      <c r="H118" s="83"/>
+      <c r="H118" s="82"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
@@ -3971,7 +3971,7 @@
       <c r="E119" s="7"/>
       <c r="F119" s="16"/>
       <c r="G119" s="29"/>
-      <c r="H119" s="83"/>
+      <c r="H119" s="82"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
@@ -3981,7 +3981,7 @@
       <c r="E120" s="7"/>
       <c r="F120" s="16"/>
       <c r="G120" s="29"/>
-      <c r="H120" s="83"/>
+      <c r="H120" s="82"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
@@ -3991,7 +3991,7 @@
       <c r="E121" s="7"/>
       <c r="F121" s="14"/>
       <c r="G121" s="29"/>
-      <c r="H121" s="83"/>
+      <c r="H121" s="82"/>
     </row>
     <row r="122" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
@@ -4001,7 +4001,7 @@
       <c r="E122" s="7"/>
       <c r="F122" s="16"/>
       <c r="G122" s="5"/>
-      <c r="H122" s="83"/>
+      <c r="H122" s="82"/>
       <c r="I122" s="7"/>
     </row>
     <row r="123" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -4012,7 +4012,7 @@
       <c r="E123" s="7"/>
       <c r="F123" s="16"/>
       <c r="G123" s="5"/>
-      <c r="H123" s="83"/>
+      <c r="H123" s="82"/>
       <c r="I123" s="7"/>
     </row>
     <row r="124" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -4023,7 +4023,7 @@
       <c r="E124" s="7"/>
       <c r="F124" s="16"/>
       <c r="G124" s="5"/>
-      <c r="H124" s="83"/>
+      <c r="H124" s="82"/>
       <c r="I124" s="7"/>
     </row>
     <row r="125" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -4034,7 +4034,7 @@
       <c r="E125" s="7"/>
       <c r="F125" s="16"/>
       <c r="G125" s="5"/>
-      <c r="H125" s="83"/>
+      <c r="H125" s="82"/>
       <c r="I125" s="7"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
       <c r="E126" s="7"/>
       <c r="F126" s="16"/>
       <c r="G126" s="29"/>
-      <c r="H126" s="83"/>
+      <c r="H126" s="82"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
@@ -4055,7 +4055,7 @@
       <c r="E127" s="7"/>
       <c r="F127" s="16"/>
       <c r="G127" s="29"/>
-      <c r="H127" s="83"/>
+      <c r="H127" s="82"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/BOM Provisional _Elisa Washer.xlsx
+++ b/BOM Provisional _Elisa Washer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D01C772-0298-4A33-8254-B32A1D94E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED1B7D4-DFBD-4874-BA0F-F32B9F718E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
